--- a/artfynd/A 33219-2024 artfynd.xlsx
+++ b/artfynd/A 33219-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119648736</v>
+        <v>119658795</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
+        <v>96866</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,42 +911,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>224364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -955,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591955</v>
+        <v>591915</v>
       </c>
       <c r="R4" t="n">
-        <v>6558301</v>
+        <v>6558309</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,9 +987,9 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1023,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119658795</v>
+        <v>119648736</v>
       </c>
       <c r="B5" t="n">
-        <v>96866</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,26 +1019,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>224364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591915</v>
+        <v>591955</v>
       </c>
       <c r="R5" t="n">
-        <v>6558309</v>
+        <v>6558301</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,9 +1111,9 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 33219-2024 artfynd.xlsx
+++ b/artfynd/A 33219-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119658473</v>
+        <v>119658576</v>
       </c>
       <c r="B2" t="n">
-        <v>108787</v>
+        <v>100171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119658576</v>
+        <v>119648736</v>
       </c>
       <c r="B3" t="n">
-        <v>100171</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,30 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -831,13 +843,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591916</v>
+        <v>591955</v>
       </c>
       <c r="R3" t="n">
-        <v>6558363</v>
+        <v>6558301</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,9 +891,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -1007,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119648736</v>
+        <v>119658473</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>108787</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,42 +1031,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1063,13 +1063,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591955</v>
+        <v>591916</v>
       </c>
       <c r="R5" t="n">
-        <v>6558301</v>
+        <v>6558363</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,9 +1111,9 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 33219-2024 artfynd.xlsx
+++ b/artfynd/A 33219-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119658576</v>
+        <v>119659206</v>
       </c>
       <c r="B2" t="n">
-        <v>100171</v>
+        <v>108787</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>220299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmtorp 250m SV, Srm</t>
+          <t>Holmtorp 200m VSV, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591916</v>
+        <v>591985</v>
       </c>
       <c r="R2" t="n">
-        <v>6558363</v>
+        <v>6558343</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -770,6 +770,11 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119648736</v>
+        <v>119658473</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
+        <v>108787</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +804,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -843,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591955</v>
+        <v>591916</v>
       </c>
       <c r="R3" t="n">
-        <v>6558301</v>
+        <v>6558363</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,9 +884,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -911,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119658795</v>
+        <v>119658576</v>
       </c>
       <c r="B4" t="n">
-        <v>96866</v>
+        <v>100171</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,19 +920,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224364</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -951,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591915</v>
+        <v>591916</v>
       </c>
       <c r="R4" t="n">
-        <v>6558309</v>
+        <v>6558363</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1019,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119658473</v>
+        <v>119648736</v>
       </c>
       <c r="B5" t="n">
-        <v>108787</v>
+        <v>97907</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1031,30 +1028,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1063,13 +1072,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591916</v>
+        <v>591955</v>
       </c>
       <c r="R5" t="n">
-        <v>6558363</v>
+        <v>6558301</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,9 +1120,9 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1131,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119659206</v>
+        <v>119658795</v>
       </c>
       <c r="B6" t="n">
-        <v>108787</v>
+        <v>96866</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,27 +1152,23 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>224364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1171,14 +1176,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Holmtorp 200m VSV, Srm</t>
+          <t>Holmtorp 250m SV, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591985</v>
+        <v>591915</v>
       </c>
       <c r="R6" t="n">
-        <v>6558343</v>
+        <v>6558309</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1226,11 +1231,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kraftledningsgata</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>

--- a/artfynd/A 33219-2024 artfynd.xlsx
+++ b/artfynd/A 33219-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119659206</v>
+        <v>119658576</v>
       </c>
       <c r="B2" t="n">
-        <v>108787</v>
+        <v>100171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,14 +715,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmtorp 200m VSV, Srm</t>
+          <t>Holmtorp 250m SV, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591985</v>
+        <v>591916</v>
       </c>
       <c r="R2" t="n">
-        <v>6558343</v>
+        <v>6558363</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -770,11 +770,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kraftledningsgata</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119658473</v>
+        <v>119648736</v>
       </c>
       <c r="B3" t="n">
-        <v>108787</v>
+        <v>97907</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,30 +799,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220299</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -836,13 +843,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591916</v>
+        <v>591955</v>
       </c>
       <c r="R3" t="n">
-        <v>6558363</v>
+        <v>6558301</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,9 +891,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -904,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119658576</v>
+        <v>119658795</v>
       </c>
       <c r="B4" t="n">
-        <v>100171</v>
+        <v>96866</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,23 +927,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>224364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -948,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591916</v>
+        <v>591915</v>
       </c>
       <c r="R4" t="n">
-        <v>6558363</v>
+        <v>6558309</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1016,10 +1019,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119648736</v>
+        <v>119659206</v>
       </c>
       <c r="B5" t="n">
-        <v>97907</v>
+        <v>108787</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,57 +1031,45 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>220299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Holmtorp 250m SV, Srm</t>
+          <t>Holmtorp 200m VSV, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591955</v>
+        <v>591985</v>
       </c>
       <c r="R5" t="n">
-        <v>6558301</v>
+        <v>6558343</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1120,9 +1111,14 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Barrblandskog</t>
+          <t>Kraftledningsgata</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1140,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119658795</v>
+        <v>119658473</v>
       </c>
       <c r="B6" t="n">
-        <v>96866</v>
+        <v>108787</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,23 +1148,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>224364</v>
+        <v>220299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591915</v>
+        <v>591916</v>
       </c>
       <c r="R6" t="n">
-        <v>6558309</v>
+        <v>6558363</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 33219-2024 artfynd.xlsx
+++ b/artfynd/A 33219-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119658576</v>
+        <v>119659070</v>
       </c>
       <c r="B2" t="n">
-        <v>100171</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93193</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,38 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>4363</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Holmtorp 250m SV, Srm</t>
+          <t>Holmtorp 300m VSV, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>591916</v>
+        <v>591881</v>
       </c>
       <c r="R2" t="n">
-        <v>6558363</v>
+        <v>6558373</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -787,54 +781,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119648736</v>
+        <v>119658473</v>
       </c>
       <c r="B3" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>220299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -843,13 +820,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>591955</v>
+        <v>591916</v>
       </c>
       <c r="R3" t="n">
-        <v>6558301</v>
+        <v>6558363</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -891,9 +868,9 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -911,35 +888,34 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119658795</v>
+        <v>119659206</v>
       </c>
       <c r="B4" t="n">
-        <v>96866</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>224364</v>
+        <v>220299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig mattlummer</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum subsp. clavatum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -947,14 +923,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Holmtorp 250m SV, Srm</t>
+          <t>Holmtorp 200m VSV, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>591915</v>
+        <v>591985</v>
       </c>
       <c r="R4" t="n">
-        <v>6558309</v>
+        <v>6558343</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1002,6 +978,11 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1019,57 +1000,64 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119659206</v>
+        <v>119648736</v>
       </c>
       <c r="B5" t="n">
-        <v>108787</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Holmtorp 200m VSV, Srm</t>
+          <t>Holmtorp 250m SV, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>591985</v>
+        <v>591955</v>
       </c>
       <c r="R5" t="n">
-        <v>6558343</v>
+        <v>6558301</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,14 +1099,9 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kraftledningsgata</t>
+          <t>Barrblandskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1136,57 +1119,68 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119658473</v>
+        <v>120785987</v>
       </c>
       <c r="B6" t="n">
-        <v>108787</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Holmtorp 250m SV, Srm</t>
+          <t>Holmtorp, knärot 250 m sv, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>591916</v>
+        <v>591954</v>
       </c>
       <c r="R6" t="n">
-        <v>6558363</v>
+        <v>6558301</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1206,6 +1200,11 @@
       <c r="W6" t="inlineStr">
         <is>
           <t>Lilla Malma</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D-Fle-0208</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1233,88 +1232,76 @@
           <t>Skogsmark</t>
         </is>
       </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Barrblandskog</t>
+        </is>
+      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
           <t>Rolf Olsson</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Rolf Olsson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120785987</v>
+        <v>119658576</v>
       </c>
       <c r="B7" t="n">
-        <v>98071</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Holmtorp, knärot 250 m sv, Srm</t>
+          <t>Holmtorp 250m SV, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>591954</v>
+        <v>591916</v>
       </c>
       <c r="R7" t="n">
-        <v>6558301</v>
+        <v>6558363</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,11 +1321,6 @@
       <c r="W7" t="inlineStr">
         <is>
           <t>Lilla Malma</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>D-Fle-0208</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1366,15 +1348,10 @@
           <t>Skogsmark</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Barrblandskog</t>
-        </is>
-      </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Rolf Olsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -1382,11 +1359,110 @@
           <t>Rolf Olsson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119658795</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97987</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>224364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vanlig mattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum subsp. clavatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Holmtorp 250m SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>591915</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6558309</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lilla Malma</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-09-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 33219-2024 artfynd.xlsx
+++ b/artfynd/A 33219-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119659070</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119658473</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,6 +1012,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119659206</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119648736</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1251,6 +1276,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120785987</t>
         </is>
       </c>
     </row>
@@ -1360,6 +1390,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119658576</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1463,8 +1498,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119658795</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>